--- a/artfynd/A 10345-2023 artfynd.xlsx
+++ b/artfynd/A 10345-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589376</v>
+        <v>121589373</v>
       </c>
       <c r="B2" t="n">
-        <v>92008</v>
+        <v>91990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647840</v>
+        <v>647813</v>
       </c>
       <c r="R2" t="n">
-        <v>7167083</v>
+        <v>7167047</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589320</v>
+        <v>121589374</v>
       </c>
       <c r="B3" t="n">
-        <v>82393</v>
+        <v>91990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>648057</v>
+        <v>647827</v>
       </c>
       <c r="R3" t="n">
-        <v>7166907</v>
+        <v>7167078</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -855,17 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589375</v>
+        <v>121589320</v>
       </c>
       <c r="B4" t="n">
-        <v>91988</v>
+        <v>82393</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,26 +903,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -936,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647828</v>
+        <v>648057</v>
       </c>
       <c r="R4" t="n">
-        <v>7167074</v>
+        <v>7166907</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,12 +961,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589373</v>
+        <v>121589376</v>
       </c>
       <c r="B5" t="n">
-        <v>91990</v>
+        <v>92008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,30 +1010,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647813</v>
+        <v>647840</v>
       </c>
       <c r="R5" t="n">
-        <v>7167047</v>
+        <v>7167083</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589319</v>
+        <v>121589375</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>91988</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,26 +1120,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>648047</v>
+        <v>647828</v>
       </c>
       <c r="R6" t="n">
-        <v>7166900</v>
+        <v>7167074</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,17 +1178,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589374</v>
+        <v>121589319</v>
       </c>
       <c r="B7" t="n">
-        <v>91990</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,26 +1226,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1259,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>647827</v>
+        <v>648047</v>
       </c>
       <c r="R7" t="n">
-        <v>7167078</v>
+        <v>7166900</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1289,12 +1284,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 10345-2023 artfynd.xlsx
+++ b/artfynd/A 10345-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589373</v>
+        <v>121589374</v>
       </c>
       <c r="B2" t="n">
         <v>91990</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647813</v>
+        <v>647827</v>
       </c>
       <c r="R2" t="n">
-        <v>7167047</v>
+        <v>7167078</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589374</v>
+        <v>121589320</v>
       </c>
       <c r="B3" t="n">
-        <v>91990</v>
+        <v>82393</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647827</v>
+        <v>648057</v>
       </c>
       <c r="R3" t="n">
-        <v>7167078</v>
+        <v>7166907</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -855,12 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589320</v>
+        <v>121589373</v>
       </c>
       <c r="B4" t="n">
-        <v>82393</v>
+        <v>91990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,26 +908,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>648057</v>
+        <v>647813</v>
       </c>
       <c r="R4" t="n">
-        <v>7166907</v>
+        <v>7167047</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -961,17 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589376</v>
+        <v>121589375</v>
       </c>
       <c r="B5" t="n">
-        <v>92008</v>
+        <v>91988</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,30 +1010,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647840</v>
+        <v>647828</v>
       </c>
       <c r="R5" t="n">
-        <v>7167083</v>
+        <v>7167074</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589375</v>
+        <v>121589376</v>
       </c>
       <c r="B6" t="n">
-        <v>91988</v>
+        <v>92008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,30 +1116,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>647828</v>
+        <v>647840</v>
       </c>
       <c r="R6" t="n">
-        <v>7167074</v>
+        <v>7167083</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 10345-2023 artfynd.xlsx
+++ b/artfynd/A 10345-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589374</v>
+        <v>121589319</v>
       </c>
       <c r="B2" t="n">
-        <v>91990</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647827</v>
+        <v>648047</v>
       </c>
       <c r="R2" t="n">
-        <v>7167078</v>
+        <v>7166900</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589320</v>
+        <v>121589374</v>
       </c>
       <c r="B3" t="n">
-        <v>82393</v>
+        <v>91998</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>648057</v>
+        <v>647827</v>
       </c>
       <c r="R3" t="n">
-        <v>7166907</v>
+        <v>7167078</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -855,17 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589373</v>
+        <v>121589375</v>
       </c>
       <c r="B4" t="n">
-        <v>91990</v>
+        <v>91996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647813</v>
+        <v>647828</v>
       </c>
       <c r="R4" t="n">
-        <v>7167047</v>
+        <v>7167074</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589375</v>
+        <v>121589320</v>
       </c>
       <c r="B5" t="n">
-        <v>91988</v>
+        <v>82400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,26 +1014,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647828</v>
+        <v>648057</v>
       </c>
       <c r="R5" t="n">
-        <v>7167074</v>
+        <v>7166907</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1072,12 +1072,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,7 +1112,7 @@
         <v>121589376</v>
       </c>
       <c r="B6" t="n">
-        <v>92008</v>
+        <v>92016</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589319</v>
+        <v>121589373</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>91998</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,26 +1231,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1254,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>648047</v>
+        <v>647813</v>
       </c>
       <c r="R7" t="n">
-        <v>7166900</v>
+        <v>7167047</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1284,17 +1289,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 10345-2023 artfynd.xlsx
+++ b/artfynd/A 10345-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589376</v>
+        <v>121589319</v>
       </c>
       <c r="B2" t="n">
-        <v>92016</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647840</v>
+        <v>648047</v>
       </c>
       <c r="R2" t="n">
-        <v>7167083</v>
+        <v>7166900</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589374</v>
+        <v>121589320</v>
       </c>
       <c r="B3" t="n">
-        <v>91998</v>
+        <v>82400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647827</v>
+        <v>648057</v>
       </c>
       <c r="R3" t="n">
-        <v>7167078</v>
+        <v>7166907</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -855,12 +860,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589373</v>
+        <v>121589375</v>
       </c>
       <c r="B4" t="n">
-        <v>91998</v>
+        <v>91996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647813</v>
+        <v>647828</v>
       </c>
       <c r="R4" t="n">
-        <v>7167047</v>
+        <v>7167074</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589375</v>
+        <v>121589373</v>
       </c>
       <c r="B5" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647828</v>
+        <v>647813</v>
       </c>
       <c r="R5" t="n">
-        <v>7167074</v>
+        <v>7167047</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589319</v>
+        <v>121589376</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>92016</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,30 +1121,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1143,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>648047</v>
+        <v>647840</v>
       </c>
       <c r="R6" t="n">
-        <v>7166900</v>
+        <v>7167083</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,17 +1183,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589320</v>
+        <v>121589374</v>
       </c>
       <c r="B7" t="n">
-        <v>82400</v>
+        <v>91998</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,26 +1231,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1254,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>648057</v>
+        <v>647827</v>
       </c>
       <c r="R7" t="n">
-        <v>7166907</v>
+        <v>7167078</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1284,17 +1289,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 10345-2023 artfynd.xlsx
+++ b/artfynd/A 10345-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589319</v>
+        <v>121589375</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>91996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>648047</v>
+        <v>647828</v>
       </c>
       <c r="R2" t="n">
-        <v>7166900</v>
+        <v>7167074</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,17 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589320</v>
+        <v>121589319</v>
       </c>
       <c r="B3" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>648057</v>
+        <v>648047</v>
       </c>
       <c r="R3" t="n">
-        <v>7166907</v>
+        <v>7166900</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589375</v>
+        <v>121589374</v>
       </c>
       <c r="B4" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,26 +908,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647828</v>
+        <v>647827</v>
       </c>
       <c r="R4" t="n">
-        <v>7167074</v>
+        <v>7167078</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589374</v>
+        <v>121589320</v>
       </c>
       <c r="B7" t="n">
-        <v>91998</v>
+        <v>82400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,26 +1226,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1259,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>647827</v>
+        <v>648057</v>
       </c>
       <c r="R7" t="n">
-        <v>7167078</v>
+        <v>7166907</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1289,12 +1284,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 10345-2023 artfynd.xlsx
+++ b/artfynd/A 10345-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589374</v>
+        <v>121589320</v>
       </c>
       <c r="B2" t="n">
-        <v>92012</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647827</v>
+        <v>648057</v>
       </c>
       <c r="R2" t="n">
-        <v>7167078</v>
+        <v>7166907</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,42 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589376</v>
+        <v>121589375</v>
       </c>
       <c r="B3" t="n">
-        <v>92030</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647840</v>
+        <v>647828</v>
       </c>
       <c r="R3" t="n">
-        <v>7167083</v>
+        <v>7167074</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -890,12 +885,7 @@
         <v>121589373</v>
       </c>
       <c r="B4" t="n">
-        <v>92012</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589319</v>
+        <v>121589374</v>
       </c>
       <c r="B5" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,26 +994,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1037,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>648047</v>
+        <v>647827</v>
       </c>
       <c r="R5" t="n">
-        <v>7166900</v>
+        <v>7167078</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1067,17 +1052,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På död stående gran</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,15 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589375</v>
+        <v>121589376</v>
       </c>
       <c r="B6" t="n">
-        <v>92010</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,26 +1095,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1148,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>647828</v>
+        <v>647840</v>
       </c>
       <c r="R6" t="n">
-        <v>7167074</v>
+        <v>7167083</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,37 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589320</v>
+        <v>121589319</v>
       </c>
       <c r="B7" t="n">
-        <v>82414</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1254,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>648057</v>
+        <v>648047</v>
       </c>
       <c r="R7" t="n">
-        <v>7166907</v>
+        <v>7166900</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 10345-2023 artfynd.xlsx
+++ b/artfynd/A 10345-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589320</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589375</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589373</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589374</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589376</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,8 +1318,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589319</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>